--- a/Template/Itinerary Template.xlsx
+++ b/Template/Itinerary Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Smart Travel PC\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84654158-5728-4C04-B481-2E1E4EEB95B0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{392E3C9E-3D21-4E06-B7C2-F5944AB25B5C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17685" yWindow="45" windowWidth="11100" windowHeight="15705" xr2:uid="{46FCF62E-0F38-40EF-B40B-6239A54C7BFA}"/>
   </bookViews>
